--- a/files/九龙-红磡-首岸第2期.xlsx
+++ b/files/九龙-红磡-首岸第2期.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,65 +39,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -109,36 +51,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -168,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -178,39 +90,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -20626,3439 +20505,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:Q29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>首岸第2期 - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>384 套</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>384 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K6" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L6" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M6" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N6" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O6" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P6" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q6" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J7" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K7" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L7" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M7" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N7" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O7" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P7" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q7" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J8" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K8" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M8" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O8" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P8" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q8" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J9" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K9" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L9" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M9" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N9" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O9" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P9" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q9" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J10" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K10" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M10" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N10" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O10" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P10" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q10" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J11" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K11" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L11" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M11" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N11" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O11" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P11" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q11" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K12" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L12" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M12" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N12" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O12" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P12" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q12" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J13" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K13" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L13" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M13" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N13" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O13" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P13" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q13" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J14" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K14" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L14" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M14" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N14" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O14" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P14" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q14" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J15" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K15" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L15" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M15" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N15" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O15" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P15" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q15" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J16" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K16" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L16" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M16" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N16" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O16" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P16" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q16" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J17" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K17" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L17" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M17" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N17" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O17" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P17" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q17" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I18" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J18" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K18" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L18" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M18" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N18" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O18" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P18" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q18" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J19" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K19" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L19" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M19" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N19" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O19" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P19" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q19" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J20" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K20" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L20" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M20" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N20" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O20" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P20" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q20" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I21" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J21" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K21" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L21" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M21" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N21" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O21" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P21" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q21" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H22" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J22" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K22" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L22" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M22" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N22" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O22" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P22" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q22" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H23" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I23" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J23" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K23" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L23" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M23" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N23" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O23" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P23" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q23" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H24" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J24" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K24" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L24" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M24" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N24" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O24" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P24" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q24" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H25" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J25" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K25" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L25" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M25" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N25" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O25" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P25" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q25" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J26" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K26" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L26" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M26" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N26" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O26" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P26" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q26" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H27" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J27" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K27" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L27" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M27" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N27" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O27" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P27" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q27" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H28" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J28" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K28" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L28" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M28" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N28" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O28" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P28" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q28" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>A | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>B | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>C | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>D | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>E | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>F | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="14" t="inlineStr">
-        <is>
-          <t>G | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>H | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="14" t="inlineStr">
-        <is>
-          <t>J | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K29" s="14" t="inlineStr">
-        <is>
-          <t>K | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L29" s="14" t="inlineStr">
-        <is>
-          <t>L | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M29" s="14" t="inlineStr">
-        <is>
-          <t>M | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N29" s="14" t="inlineStr">
-        <is>
-          <t>N | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O29" s="14" t="inlineStr">
-        <is>
-          <t>P | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P29" s="14" t="inlineStr">
-        <is>
-          <t>Q | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q29" s="14" t="inlineStr">
-        <is>
-          <t>R | 暂无 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-红磡-首岸第2期.xlsx
+++ b/files/九龙-红磡-首岸第2期.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,8 +40,85 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +129,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -90,6 +198,51 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -20505,4 +20658,3439 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M4" s="17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N4" s="17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O4" s="17" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P4" s="17" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="Q4" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K5" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L5" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M5" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N5" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O5" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P5" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q5" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L6" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M6" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N6" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O6" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P6" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q6" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K7" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M7" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N7" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O7" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P7" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q7" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L8" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N8" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O8" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P8" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q8" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M9" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N9" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O9" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P9" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q9" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J10" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L10" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M10" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N10" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O10" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P10" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q10" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M11" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N11" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O11" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P11" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q11" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J12" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M12" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N12" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O12" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P12" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q12" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M13" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N13" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O13" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P13" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q13" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J14" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K14" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L14" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M14" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N14" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O14" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P14" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q14" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J15" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K15" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M15" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N15" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O15" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P15" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q15" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J16" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K16" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L16" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M16" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N16" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O16" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P16" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q16" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J17" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K17" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L17" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M17" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N17" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O17" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P17" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q17" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I18" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J18" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K18" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L18" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M18" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N18" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O18" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P18" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q18" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I19" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J19" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K19" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L19" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M19" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N19" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O19" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P19" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q19" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J20" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K20" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L20" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M20" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N20" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O20" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P20" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q20" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I21" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K21" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L21" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M21" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N21" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O21" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P21" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q21" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I22" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K22" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L22" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M22" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N22" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O22" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P22" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q22" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H23" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I23" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J23" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K23" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L23" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M23" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N23" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O23" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P23" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q23" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I24" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K24" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L24" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M24" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N24" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O24" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P24" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q24" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I25" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K25" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L25" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M25" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N25" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O25" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P25" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q25" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H26" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I26" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J26" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K26" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L26" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M26" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N26" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O26" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P26" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q26" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I27" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K27" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L27" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M27" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N27" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O27" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P27" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q27" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>A | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>B | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>C | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>D | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>E | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>F | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="18" t="inlineStr">
+        <is>
+          <t>G | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I28" s="18" t="inlineStr">
+        <is>
+          <t>H | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J28" s="18" t="inlineStr">
+        <is>
+          <t>J | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K28" s="18" t="inlineStr">
+        <is>
+          <t>K | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L28" s="18" t="inlineStr">
+        <is>
+          <t>L | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M28" s="18" t="inlineStr">
+        <is>
+          <t>M | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N28" s="18" t="inlineStr">
+        <is>
+          <t>N | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O28" s="18" t="inlineStr">
+        <is>
+          <t>P | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P28" s="18" t="inlineStr">
+        <is>
+          <t>Q | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q28" s="18" t="inlineStr">
+        <is>
+          <t>R | 0呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>